--- a/research/traditional_assets/database/data/venezuela/venezuela_steel.xlsx
+++ b/research/traditional_assets/database/data/venezuela/venezuela_steel.xlsx
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.2750143103365023</v>
+        <v>0.3582076658662377</v>
       </c>
       <c r="AB2">
-        <v>0.2750143103365023</v>
+        <v>0.3582076658662377</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.2750143103365023</v>
+        <v>0.3582076658662377</v>
       </c>
       <c r="AB3">
-        <v>0.2750143103365023</v>
+        <v>0.3582076658662377</v>
       </c>
       <c r="AD3">
         <v>0</v>

--- a/research/traditional_assets/database/data/venezuela/venezuela_steel.xlsx
+++ b/research/traditional_assets/database/data/venezuela/venezuela_steel.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>10.1</v>
+        <v>-1.15</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,58 +606,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>3.401709401709402</v>
+      </c>
+      <c r="W2">
+        <v>-0.001251360174102285</v>
       </c>
       <c r="X2">
-        <v>0.3582076658662377</v>
+        <v>2.162505359480311</v>
+      </c>
+      <c r="Y2">
+        <v>-2.163756719654414</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>-0.0003304621052061325</v>
       </c>
       <c r="AB2">
-        <v>0.3582076658662377</v>
+        <v>0.3311833141603037</v>
+      </c>
+      <c r="AC2">
+        <v>-0.3315137762655098</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.9103448275862069</v>
+      </c>
+      <c r="AI2">
+        <v>0.006422038186260731</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.8710033076074972</v>
+      </c>
+      <c r="AK2">
+        <v>0.004279755132997454</v>
       </c>
       <c r="AL2">
-        <v>10.4</v>
+        <v>7.87</v>
       </c>
       <c r="AM2">
-        <v>1.380000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-22.16417910447761</v>
       </c>
       <c r="AO2">
-        <v>-0.1115384615384615</v>
+        <v>-0.03875476493011436</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
+        <v>-14.73880597014925</v>
       </c>
       <c r="AQ2">
-        <v>-0.8405797101449271</v>
+        <v>-0.03875476493011436</v>
       </c>
     </row>
     <row r="3">
@@ -668,7 +689,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Siderúrgica Venezolana "Sivensa", S.A. (CCSE:1SVS)</t>
+          <t>Siderúrgica Venezolana "Sivensa", S.A. (CCSE:SVS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -677,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>10.1</v>
+        <v>-1.15</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -686,7 +707,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -695,58 +716,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>3.401709401709402</v>
+      </c>
+      <c r="W3">
+        <v>-0.001251360174102285</v>
       </c>
       <c r="X3">
-        <v>0.3582076658662377</v>
+        <v>2.162505359480311</v>
+      </c>
+      <c r="Y3">
+        <v>-2.163756719654414</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-0.0003304621052061325</v>
       </c>
       <c r="AB3">
-        <v>0.3582076658662377</v>
+        <v>0.3311833141603037</v>
+      </c>
+      <c r="AC3">
+        <v>-0.3315137762655098</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.9103448275862069</v>
+      </c>
+      <c r="AI3">
+        <v>0.006422038186260731</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.8710033076074972</v>
+      </c>
+      <c r="AK3">
+        <v>0.004279755132997454</v>
       </c>
       <c r="AL3">
-        <v>10.4</v>
+        <v>7.87</v>
       </c>
       <c r="AM3">
-        <v>1.380000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-22.16417910447761</v>
       </c>
       <c r="AO3">
-        <v>-0.1115384615384615</v>
+        <v>-0.03875476493011436</v>
       </c>
       <c r="AP3">
-        <v>-0</v>
+        <v>-14.73880597014925</v>
       </c>
       <c r="AQ3">
-        <v>-0.8405797101449271</v>
+        <v>-0.03875476493011436</v>
       </c>
     </row>
   </sheetData>
